--- a/data/trans_dic/P68-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P68-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 22,73</t>
+          <t>14,62; 23,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 22,82</t>
+          <t>14,21; 23,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 22,38</t>
+          <t>12,84; 22,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 17,48</t>
+          <t>10,3; 17,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 27,51</t>
+          <t>16,6; 27,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 29,56</t>
+          <t>17,1; 29,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 28,64</t>
+          <t>16,72; 28,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,38; 23,25</t>
+          <t>15,42; 23,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 23,34</t>
+          <t>16,22; 22,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 23,82</t>
+          <t>16,54; 24,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,81; 22,92</t>
+          <t>15,64; 22,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 18,87</t>
+          <t>13,36; 18,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 21,24</t>
+          <t>11,35; 20,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,28</t>
+          <t>10,42; 19,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,48</t>
+          <t>8,66; 17,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,45; 21,62</t>
+          <t>12,59; 21,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 23,26</t>
+          <t>13,16; 23,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 23,33</t>
+          <t>10,58; 22,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 21,5</t>
+          <t>10,89; 21,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,07; 22,22</t>
+          <t>12,97; 22,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 20,13</t>
+          <t>13,42; 20,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 19,23</t>
+          <t>11,42; 18,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 17,9</t>
+          <t>10,75; 17,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 20,1</t>
+          <t>13,97; 20,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,7; 31,67</t>
+          <t>22,22; 32,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,14; 34,07</t>
+          <t>23,41; 33,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,33; 37,96</t>
+          <t>24,61; 37,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 25,46</t>
+          <t>2,61; 26,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 41,12</t>
+          <t>17,2; 41,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,7; 39,33</t>
+          <t>22,3; 39,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 25,2</t>
+          <t>7,11; 24,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 34,32</t>
+          <t>16,83; 34,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,69; 31,14</t>
+          <t>22,73; 31,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 33,82</t>
+          <t>24,66; 34,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,08; 32,66</t>
+          <t>21,7; 32,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 25,86</t>
+          <t>4,66; 25,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 32,17</t>
+          <t>25,36; 32,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 32,75</t>
+          <t>23,48; 31,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,12; 32,69</t>
+          <t>24,03; 32,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 28,51</t>
+          <t>20,11; 28,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 21,38</t>
+          <t>12,62; 20,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,77; 28,12</t>
+          <t>17,94; 27,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 27,85</t>
+          <t>18,57; 27,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,59; 28,67</t>
+          <t>21,69; 29,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,33; 27,62</t>
+          <t>22,33; 27,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,26; 29,01</t>
+          <t>22,23; 28,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,04; 29,07</t>
+          <t>23,13; 29,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 27,77</t>
+          <t>21,69; 27,37</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,59; 42,33</t>
+          <t>27,58; 42,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,06; 33,79</t>
+          <t>18,75; 34,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,37; 42,85</t>
+          <t>28,89; 43,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,8; 28,35</t>
+          <t>16,89; 29,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,78; 38,25</t>
+          <t>25,08; 38,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,24; 32,05</t>
+          <t>18,97; 32,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,45; 30,95</t>
+          <t>18,14; 29,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,86; 52,25</t>
+          <t>18,85; 50,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,06; 38,14</t>
+          <t>27,96; 37,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,93; 30,41</t>
+          <t>20,83; 31,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,43; 34,47</t>
+          <t>25,05; 34,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,72; 40,59</t>
+          <t>20,98; 40,88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,01; 27,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,21; 25,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,46; 27,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,5; 21,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,23; 24,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,11; 25,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,56; 23,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,15; 30,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,24; 25,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,41; 24,97</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,49; 24,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,24; 23,81</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23,36%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>23,0; 27,07</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>21,2; 25,66</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22,58; 27,28</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 21,09</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19,17; 24,41</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,07; 25,82</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,69; 23,54</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>21,09; 30,36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22,2; 25,35</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>21,42; 24,82</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21,58; 25,06</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,2; 23,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51911; 81329</t>
+          <t>52303; 82336</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41120; 69115</t>
+          <t>43018; 70281</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33655; 62050</t>
+          <t>35589; 62950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33270; 60120</t>
+          <t>35409; 59743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36455; 59736</t>
+          <t>36053; 60072</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32680; 57464</t>
+          <t>33241; 56768</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35087; 60726</t>
+          <t>35464; 59768</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48345; 73091</t>
+          <t>48491; 72364</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94116; 134203</t>
+          <t>93237; 130230</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82762; 118456</t>
+          <t>82253; 119613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77357; 112151</t>
+          <t>76544; 111270</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89479; 124255</t>
+          <t>87942; 124379</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31170; 57324</t>
+          <t>30619; 56070</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25858; 49655</t>
+          <t>26823; 51336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21072; 42493</t>
+          <t>21048; 43370</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37379; 64897</t>
+          <t>37785; 65803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30219; 54369</t>
+          <t>30759; 54180</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17772; 38976</t>
+          <t>17666; 38355</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20272; 40464</t>
+          <t>20508; 40002</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32492; 55267</t>
+          <t>32243; 55008</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68583; 101359</t>
+          <t>67612; 105674</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48859; 81664</t>
+          <t>48504; 78989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45823; 77192</t>
+          <t>46378; 75234</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76865; 110352</t>
+          <t>76708; 110839</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85766; 119678</t>
+          <t>83961; 121058</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64930; 95593</t>
+          <t>65678; 95000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52228; 81480</t>
+          <t>52839; 80794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14359; 124036</t>
+          <t>12734; 126754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9850; 23390</t>
+          <t>9784; 23576</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24030; 43552</t>
+          <t>24690; 43514</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4992; 16934</t>
+          <t>4779; 16537</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12555; 24600</t>
+          <t>12064; 24556</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98652; 135369</t>
+          <t>98817; 135823</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95847; 132355</t>
+          <t>96498; 134491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62226; 92067</t>
+          <t>61172; 91840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21172; 144510</t>
+          <t>26032; 143960</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>177019; 225681</t>
+          <t>177875; 228482</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100307; 139143</t>
+          <t>99774; 135238</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116356; 157652</t>
+          <t>115887; 157622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112595; 157344</t>
+          <t>110989; 156468</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39110; 65196</t>
+          <t>38484; 63561</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53475; 84605</t>
+          <t>53984; 83185</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68197; 102203</t>
+          <t>68142; 100444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90913; 120712</t>
+          <t>91318; 122675</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>224732; 277945</t>
+          <t>224777; 280600</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161581; 210551</t>
+          <t>161315; 209619</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>195711; 246877</t>
+          <t>196428; 247850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>214623; 270182</t>
+          <t>211090; 266314</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50473; 77432</t>
+          <t>50452; 77914</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30667; 51654</t>
+          <t>28669; 52281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56677; 82693</t>
+          <t>55740; 83388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39207; 66160</t>
+          <t>39417; 69173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51714; 79817</t>
+          <t>52325; 80239</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32042; 56287</t>
+          <t>33326; 56603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36278; 60861</t>
+          <t>35664; 58927</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76804; 192341</t>
+          <t>69393; 184716</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>109881; 149350</t>
+          <t>109491; 147819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68751; 99908</t>
+          <t>68442; 102834</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99075; 134294</t>
+          <t>97591; 134374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>124652; 244157</t>
+          <t>126210; 245869</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331452</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>434785; 510365</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>300958; 365159</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>316701; 384864</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>220486; 403355</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>196389; 247541</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>190759; 242807</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>191391; 243020</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>301172; 438530</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>647587; 743145</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>506861; 591211</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>524653; 608912</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>542552; 795463</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>331452</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>215828</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>547280</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>434675; 511692</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>300778; 363978</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>318451; 384700</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>204144; 404121</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>195809; 249326</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>190384; 244971</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>192722; 242708</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>300271; 432237</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>646303; 737942</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>506992; 587553</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>526758; 611851</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>541036; 788807</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P68-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P68-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,62; 23,01</t>
+          <t>14,02; 22,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 23,21</t>
+          <t>13,73; 23,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,84; 22,7</t>
+          <t>12,95; 21,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,3; 17,37</t>
+          <t>10,29; 18,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 27,66</t>
+          <t>16,39; 27,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,1; 29,2</t>
+          <t>16,79; 29,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 28,19</t>
+          <t>16,4; 27,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,42; 23,02</t>
+          <t>15,43; 23,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 22,65</t>
+          <t>16,03; 23,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,54; 24,06</t>
+          <t>16,28; 23,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 22,74</t>
+          <t>15,43; 22,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 18,89</t>
+          <t>13,35; 19,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 20,78</t>
+          <t>11,34; 20,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 19,93</t>
+          <t>10,32; 19,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,84</t>
+          <t>8,59; 17,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 21,92</t>
+          <t>11,79; 21,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 23,17</t>
+          <t>13,05; 22,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 22,96</t>
+          <t>10,48; 22,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 21,25</t>
+          <t>10,78; 21,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 22,12</t>
+          <t>13,25; 21,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 20,98</t>
+          <t>13,77; 20,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 18,6</t>
+          <t>12,02; 18,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 17,44</t>
+          <t>10,82; 17,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 20,19</t>
+          <t>13,66; 19,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 32,04</t>
+          <t>22,22; 31,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,41; 33,86</t>
+          <t>23,61; 34,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,61; 37,64</t>
+          <t>24,62; 38,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 26,02</t>
+          <t>17,0; 28,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 41,45</t>
+          <t>17,27; 41,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,3; 39,3</t>
+          <t>21,5; 39,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 24,61</t>
+          <t>7,4; 24,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 34,26</t>
+          <t>17,61; 34,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,73; 31,24</t>
+          <t>22,5; 31,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,66; 34,37</t>
+          <t>24,74; 33,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,7; 32,58</t>
+          <t>21,9; 32,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 25,76</t>
+          <t>18,9; 28,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,36; 32,57</t>
+          <t>25,51; 32,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,48; 31,83</t>
+          <t>23,32; 32,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,03; 32,68</t>
+          <t>23,98; 32,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 28,35</t>
+          <t>21,56; 29,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 20,84</t>
+          <t>12,69; 20,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 27,64</t>
+          <t>18,03; 27,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,57; 27,37</t>
+          <t>18,71; 27,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,69; 29,13</t>
+          <t>20,85; 27,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,33; 27,88</t>
+          <t>22,26; 27,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,23; 28,88</t>
+          <t>22,43; 29,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,13; 29,18</t>
+          <t>22,98; 29,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,69; 27,37</t>
+          <t>22,11; 27,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,58; 42,59</t>
+          <t>28,04; 43,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 34,2</t>
+          <t>19,31; 34,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,89; 43,21</t>
+          <t>28,92; 42,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 29,64</t>
+          <t>16,85; 27,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,08; 38,46</t>
+          <t>25,2; 38,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,97; 32,23</t>
+          <t>18,56; 32,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,14; 29,97</t>
+          <t>18,4; 30,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 50,18</t>
+          <t>28,45; 37,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,96; 37,75</t>
+          <t>28,39; 38,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 31,3</t>
+          <t>21,1; 31,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,05; 34,49</t>
+          <t>25,07; 34,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,98; 40,88</t>
+          <t>23,88; 30,95</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,01; 27,0</t>
+          <t>23,04; 27,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,21; 25,74</t>
+          <t>21,07; 25,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,29</t>
+          <t>22,39; 27,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,5; 21,05</t>
+          <t>18,4; 22,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,23</t>
+          <t>18,7; 24,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,11; 25,59</t>
+          <t>20,1; 25,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,56; 23,57</t>
+          <t>18,43; 23,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,15; 30,8</t>
+          <t>21,4; 25,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,24; 25,53</t>
+          <t>22,29; 25,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,41; 24,97</t>
+          <t>21,35; 24,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,49; 24,94</t>
+          <t>21,52; 25,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,81</t>
+          <t>20,51; 23,18</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>62032</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>105106</t>
+          <t>114070</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52303; 82336</t>
+          <t>50159; 80090</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43018; 70281</t>
+          <t>41564; 70097</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35589; 62950</t>
+          <t>35905; 60521</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35409; 59743</t>
+          <t>38557; 68991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36053; 60072</t>
+          <t>35585; 59672</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33241; 56768</t>
+          <t>32644; 57123</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35464; 59768</t>
+          <t>34780; 58943</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48491; 72364</t>
+          <t>51804; 77465</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93237; 130230</t>
+          <t>92158; 132300</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82253; 119613</t>
+          <t>80965; 117703</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76544; 111270</t>
+          <t>75491; 110311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87942; 124379</t>
+          <t>94832; 135052</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>52059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>45454</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92937</t>
+          <t>97513</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30619; 56070</t>
+          <t>30593; 55442</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26823; 51336</t>
+          <t>26569; 50562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21048; 43370</t>
+          <t>20886; 42201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37785; 65803</t>
+          <t>37433; 66738</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30759; 54180</t>
+          <t>30507; 53285</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17666; 38355</t>
+          <t>17507; 38277</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20508; 40002</t>
+          <t>20297; 40875</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32243; 55008</t>
+          <t>35790; 56989</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67612; 105674</t>
+          <t>69338; 102541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48504; 78989</t>
+          <t>51052; 80618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46378; 75234</t>
+          <t>46665; 75241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76708; 110839</t>
+          <t>80256; 116413</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58523</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76362</t>
+          <t>81942</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83961; 121058</t>
+          <t>83982; 119678</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65678; 95000</t>
+          <t>66235; 96507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52839; 80794</t>
+          <t>52846; 82352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12734; 126754</t>
+          <t>45731; 77325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9784; 23576</t>
+          <t>9826; 23508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24690; 43514</t>
+          <t>23801; 44232</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4779; 16537</t>
+          <t>4973; 16754</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12064; 24556</t>
+          <t>14238; 27612</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98817; 135823</t>
+          <t>97806; 135134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96498; 134491</t>
+          <t>96812; 132834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61172; 91840</t>
+          <t>61736; 91650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26032; 143960</t>
+          <t>66110; 99828</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133218</t>
+          <t>153762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>105758</t>
+          <t>113765</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>238976</t>
+          <t>267527</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>177875; 228482</t>
+          <t>178927; 228313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>99774; 135238</t>
+          <t>99106; 138019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115887; 157622</t>
+          <t>115645; 157954</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110989; 156468</t>
+          <t>132184; 179237</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38484; 63561</t>
+          <t>38690; 63237</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53984; 83185</t>
+          <t>54266; 83789</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68142; 100444</t>
+          <t>68659; 101738</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91318; 122675</t>
+          <t>98475; 130617</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>224777; 280600</t>
+          <t>224023; 280557</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161315; 209619</t>
+          <t>162798; 214124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196428; 247850</t>
+          <t>195186; 249626</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>211090; 266314</t>
+          <t>239977; 297019</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51170</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>101653</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>178417</t>
+          <t>167319</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50452; 77914</t>
+          <t>51300; 78732</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28669; 52281</t>
+          <t>29518; 52079</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55740; 83388</t>
+          <t>55802; 82671</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39417; 69173</t>
+          <t>51030; 84545</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52325; 80239</t>
+          <t>52576; 81097</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33326; 56603</t>
+          <t>32604; 56736</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35664; 58927</t>
+          <t>36184; 59358</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>69393; 184716</t>
+          <t>87434; 115863</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>109491; 147819</t>
+          <t>111187; 149001</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68442; 102834</t>
+          <t>69307; 103250</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97591; 134374</t>
+          <t>97652; 136269</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>126210; 245869</t>
+          <t>145701; 188871</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>352292</t>
+          <t>343362</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>691797</t>
+          <t>728371</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>434785; 510365</t>
+          <t>435450; 511111</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>300958; 365159</t>
+          <t>298880; 363016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316701; 384864</t>
+          <t>315797; 384409</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>220486; 403355</t>
+          <t>345408; 424488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>196389; 247541</t>
+          <t>190991; 247029</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>190759; 242807</t>
+          <t>190709; 245637</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>191391; 243020</t>
+          <t>190079; 242483</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>301172; 438530</t>
+          <t>313838; 372434</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>647587; 743145</t>
+          <t>648881; 735848</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>506861; 591211</t>
+          <t>505548; 585496</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>524653; 608912</t>
+          <t>525395; 610353</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>542552; 795463</t>
+          <t>685733; 774905</t>
         </is>
       </c>
     </row>
